--- a/MainTop/18.03.2026 Таня Новые ВБ/штрих.xlsx
+++ b/MainTop/18.03.2026 Таня Новые ВБ/штрих.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\18.03.2026 Таня Новые ВБ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\18.03.2026 Таня Новые ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD7395E-3FAE-43B7-A8D7-54599CD14EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1037DB1-974D-468E-901A-C8D2979B8A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -202,9 +202,6 @@
     <t>Термонаклейка Астронавт и время космос</t>
   </si>
   <si>
-    <t xml:space="preserve">Термонаклейка Астронавт и часы </t>
-  </si>
-  <si>
     <t>Термонаклейка Горы и красная луна</t>
   </si>
   <si>
@@ -299,6 +296,9 @@
   </si>
   <si>
     <t>Термонаклейка Черный кот в цветах вариант2</t>
+  </si>
+  <si>
+    <t>Термонаклейка Астронавт и часы</t>
   </si>
 </sst>
 </file>
@@ -1286,7 +1286,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B50" s="3">
         <v>6</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="B57" s="3">
         <v>6</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" s="3">
         <v>6</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" s="3">
         <v>6</v>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" s="3">
         <v>6</v>
@@ -1418,7 +1418,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" s="3">
         <v>6</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" s="3">
         <v>6</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" s="3">
         <v>6</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" s="3">
         <v>6</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" s="3">
         <v>6</v>
@@ -1478,7 +1478,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" s="3">
         <v>6</v>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" s="3">
         <v>6</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" s="3">
         <v>6</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" s="3">
         <v>6</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" s="3">
         <v>6</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" s="3">
         <v>6</v>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" s="3">
         <v>6</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" s="3">
         <v>6</v>
@@ -1574,7 +1574,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" s="3">
         <v>6</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" s="3">
         <v>6</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" s="3">
         <v>6</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" s="3">
         <v>6</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" s="3">
         <v>6</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" s="3">
         <v>6</v>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" s="3">
         <v>6</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" s="3">
         <v>6</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" s="3">
         <v>6</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" s="3">
         <v>6</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" s="3">
         <v>6</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" s="3">
         <v>6</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" s="3">
         <v>6</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" s="3">
         <v>6</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B88" s="3">
         <v>6</v>
